--- a/tables/table_app.xlsx
+++ b/tables/table_app.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wmj\Desktop\0228\科研数据会诊室 · 图书情报机构的核心能力重塑\manuscript\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wmj\Desktop\research-data-clinic\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15738B5D-886A-482C-B353-EAACC7FAA534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18B1B29-C079-404B-842D-C4A9F1A8E895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,11 +79,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>本文稿件与补充材料</t>
+    <t>开放课程与 GitHub 代码仓库</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>开放课程与 GitHub 代码仓库</t>
+    <t>本文档的 Quarto 源文件与补充材料</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -508,7 +508,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>4</v>
@@ -556,7 +556,7 @@
         <v>15</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>14</v>

--- a/tables/table_app.xlsx
+++ b/tables/table_app.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wmj\Desktop\research-data-clinic\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18B1B29-C079-404B-842D-C4A9F1A8E895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B53C0BB-B71E-4002-9FC2-993DBFCCBB2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>序号</t>
   </si>
@@ -84,6 +84,18 @@
   </si>
   <si>
     <t>本文档的 Quarto 源文件与补充材料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料 6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>典型会诊案例（方法论部分）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/perlatex/research-data-clinic/case</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -482,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.6640625" customWidth="1"/>
@@ -551,21 +563,28 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:4" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -577,6 +596,11 @@
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -585,9 +609,10 @@
     <hyperlink ref="C3" r:id="rId2" xr:uid="{D1B251E9-EF25-42E1-AD40-79A441B5D5FE}"/>
     <hyperlink ref="C4" r:id="rId3" xr:uid="{34DE6D06-9CFE-4D18-8BFC-EC7698EDB01A}"/>
     <hyperlink ref="C5" r:id="rId4" xr:uid="{66A09183-CB1B-4E16-8E0F-6614B3C78E39}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{17F452C5-169B-4625-AD3D-E84BD6539447}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{17F452C5-169B-4625-AD3D-E84BD6539447}"/>
+    <hyperlink ref="C6" r:id="rId6" xr:uid="{9FC370CE-A90A-4A64-9D5B-CA36111830FD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
--- a/tables/table_app.xlsx
+++ b/tables/table_app.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wmj\Desktop\research-data-clinic\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B53C0BB-B71E-4002-9FC2-993DBFCCBB2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F95BBCCE-2B26-4C82-B4A8-5C2AFE9490C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>序号</t>
   </si>
@@ -36,28 +36,16 @@
     <t>链接</t>
   </si>
   <si>
-    <t>材料 1</t>
-  </si>
-  <si>
     <t>https://github.com/perlatex</t>
   </si>
   <si>
-    <t>材料 2</t>
-  </si>
-  <si>
     <t>自编在线教材</t>
   </si>
   <si>
     <t>https://bookdown.org/wangminjie/R4DS/</t>
   </si>
   <si>
-    <t>材料 3</t>
-  </si>
-  <si>
     <t>https://lib.sicnu.edu.cn/navigation/web_list1?c_id=493300E5-21C4-B5D5-F156-CCB9BF2C7D2B&amp;cataID=1yoI6LsHraDItEc&amp;vp=1-d14c-a2fe-navigation-79db-10ad</t>
-  </si>
-  <si>
-    <t>材料 4</t>
   </si>
   <si>
     <t>https://lib.sicnu.edu.cn/navigation/web_detailspage1?id=BtQdh6QubfTBXHFL&amp;c_id=493300E5-21C4-B5D5-F156-CCB9BF2C7D2B&amp;cataID=PRXD6QubdnCfhZi</t>
@@ -75,10 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>材料 5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>开放课程与 GitHub 代码仓库</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -87,16 +71,21 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>材料 6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>典型会诊案例（方法论部分）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>https://github.com/perlatex/research-data-clinic/case</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开展情况</t>
+  </si>
+  <si>
+    <t>知识沉淀</t>
+  </si>
+  <si>
+    <t>本稿件</t>
   </si>
 </sst>
 </file>
@@ -184,7 +173,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -196,22 +185,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -503,87 +486,87 @@
     <col min="4" max="4" width="29.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="33.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:4" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="3" spans="1:4" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" ht="34.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>14</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -605,10 +588,10 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{1199D2B3-9B6D-4A2B-B2AA-2A6A527AC78B}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{D1B251E9-EF25-42E1-AD40-79A441B5D5FE}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{34DE6D06-9CFE-4D18-8BFC-EC7698EDB01A}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{66A09183-CB1B-4E16-8E0F-6614B3C78E39}"/>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{1199D2B3-9B6D-4A2B-B2AA-2A6A527AC78B}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{D1B251E9-EF25-42E1-AD40-79A441B5D5FE}"/>
+    <hyperlink ref="C2" r:id="rId3" xr:uid="{34DE6D06-9CFE-4D18-8BFC-EC7698EDB01A}"/>
+    <hyperlink ref="C3" r:id="rId4" xr:uid="{66A09183-CB1B-4E16-8E0F-6614B3C78E39}"/>
     <hyperlink ref="C7" r:id="rId5" xr:uid="{17F452C5-169B-4625-AD3D-E84BD6539447}"/>
     <hyperlink ref="C6" r:id="rId6" xr:uid="{9FC370CE-A90A-4A64-9D5B-CA36111830FD}"/>
   </hyperlinks>

--- a/tables/table_app.xlsx
+++ b/tables/table_app.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wmj\Desktop\research-data-clinic\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F95BBCCE-2B26-4C82-B4A8-5C2AFE9490C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34EAB3D-F059-447A-B9E8-8107ABD57DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
-    <t>序号</t>
-  </si>
-  <si>
     <t>材料名称</t>
   </si>
   <si>
@@ -86,6 +83,10 @@
   </si>
   <si>
     <t>本稿件</t>
+  </si>
+  <si>
+    <t>类别</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -488,85 +489,85 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
       </c>
       <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:4" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:4" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>4</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>5</v>
       </c>
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>14</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2"/>
     </row>
